--- a/output/problem1_results.xlsx
+++ b/output/problem1_results.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,20 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
         <bgColor rgb="00BDD7EE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B084"/>
-        <bgColor rgb="00F4B084"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -667,43 +658,43 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0.385</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.9167</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.625</v>
+        <v>0.7143</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.8409</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0.842</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.3101</v>
+        <v>0.375</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.3125</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>1</v>
@@ -712,41 +703,41 @@
         <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>1</v>
+        <v>0.4708</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>67.72</v>
+        <v>43.39</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>62.63</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>54.47</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>72.39</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.1073</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.2768</v>
+        <v>0.2143</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.1637</v>
+        <v>0.2572</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.0868</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>0.3847</v>
+        <v>0.3294</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>65.61</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -765,40 +756,40 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.6891</v>
+        <v>0.337</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1</v>
+        <v>0.7528</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1389</v>
+        <v>0.4167</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.2221</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.7045</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.8471</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.2965</v>
+        <v>0.4192</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1562</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>1</v>
@@ -807,44 +798,44 @@
         <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.2577</v>
+        <v>0.75</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>1</v>
+        <v>0.3984</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>61.4</v>
+        <v>32.44</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>67.23999999999999</v>
+        <v>60.1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>76.41</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.1353</v>
+        <v>0.3612</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>0.1855</v>
+        <v>0.1481</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>0.0854</v>
+        <v>0.1024</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.1001</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.4938</v>
+        <v>0.3257</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>68.8</v>
+        <v>55.85</v>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -863,86 +854,86 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2976</v>
+        <v>0.2653</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>0.928</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.9375</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.6385</v>
+        <v>0.6843</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.2648</v>
+        <v>0.375</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.1562</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.9722</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>1</v>
+        <v>0.7378</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>82.31999999999999</v>
+        <v>57.58</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>74.68000000000001</v>
+        <v>60.1</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>78.42</v>
+        <v>66.09</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>81.15000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.1038</v>
+        <v>0.1623</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>0.0453</v>
+        <v>0.2405</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>0.0423</v>
+        <v>0.1621</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.1272</v>
+        <v>0.1668</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>0.6813</v>
+        <v>0.2683</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>78.03</v>
+        <v>61.26</v>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -961,86 +952,86 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.9522</v>
+        <v>0.3153</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1</v>
+        <v>0.6818</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.8571</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.625</v>
+        <v>0.6944</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.4988</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.95</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0.8409</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.0435</v>
+        <v>0.0793</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.375</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>1</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>77.34</v>
+        <v>38.28</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>61.32</v>
+        <v>69</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>53.43</v>
+        <v>69.02</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>64.58</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>0.027</v>
+        <v>0.1687</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.2227</v>
+        <v>0.3073</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.3629</v>
+        <v>0.1504</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.0335</v>
+        <v>0.0477</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>0.3538</v>
+        <v>0.3259</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>66.83</v>
+        <v>59.98</v>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -1059,86 +1050,86 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3378</v>
+        <v>0.28</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1</v>
+        <v>0.7197</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.9125</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.875</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.8946</v>
+        <v>0.4757</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.3372</v>
+        <v>0.428</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>0.8333</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
+        <v>0.6934</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>77.06999999999999</v>
+        <v>44.38</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>51.08</v>
+        <v>86.37</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>61.84</v>
+        <v>72.28</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>81.15000000000001</v>
+        <v>33.07</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>0.24</v>
+        <v>0.1978</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>0.1482</v>
+        <v>0.1103</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>0.0502</v>
+        <v>0.082</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.2131</v>
+        <v>0.1764</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>0.3485</v>
+        <v>0.4334</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>63.03</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -1157,84 +1148,84 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>0.3278</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>0.8949</v>
       </c>
       <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>0.6944</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="2" t="n">
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.9091</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0.5493</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0.1596</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0.5694</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.5155</v>
+        <v>0.9375</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>83.98999999999999</v>
+        <v>58.26</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>67</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>76.19</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>86.62</v>
+        <v>55.45</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>0.0145</v>
+        <v>0.0857</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>0.0562</v>
+        <v>0.2672</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>0.1947</v>
+        <v>0.1365</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.3705</v>
+        <v>0.1215</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.3641</v>
+        <v>0.3891</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>75.13</v>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1255,84 +1246,84 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4108</v>
+        <v>0.2586</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.8158</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.6944</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.4842</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.694</v>
+        <v>0.7491</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.2695</v>
+        <v>0.4272</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.6186</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>1</v>
+        <v>0.6993</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>71.61</v>
+        <v>30.73</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>48.49</v>
+        <v>72.59</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>55.62</v>
+        <v>74.06</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>87.12</v>
+        <v>73.88</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>0.2187</v>
+        <v>0.2022</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>0.1469</v>
+        <v>0.2354</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.2773</v>
+        <v>0.1415</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.0585</v>
+        <v>0.0506</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.2987</v>
+        <v>0.3703</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>59.98</v>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
+        <v>61.26</v>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -1353,40 +1344,40 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.4323</v>
+        <v>0.3375</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1</v>
+        <v>0.9517</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.7</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.2083</v>
+        <v>0.9375</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.1132</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1</v>
+        <v>0.8409</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.2665</v>
+        <v>0.3839</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.6667</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>1</v>
@@ -1395,44 +1386,44 @@
         <v>1</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>0.5669999999999999</v>
+        <v>1</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>61.52</v>
+        <v>47.14</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>31.15</v>
+        <v>86.16</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>69.25</v>
+        <v>75.36</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>86.8</v>
+        <v>68.09</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>0.4243</v>
+        <v>0.121</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.1694</v>
+        <v>0.132</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>0.0989</v>
+        <v>0.0723</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>0.2316</v>
+        <v>0.5643</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>51.04</v>
+        <v>71.8</v>
       </c>
       <c r="AD9" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -1451,86 +1442,86 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.4906</v>
+        <v>0.302</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.9597</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.7692</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.3427</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0.7766</v>
+        <v>0.7418</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.0481</v>
+        <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0</v>
+        <v>0.0329</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>0.7732</v>
+        <v>1</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>1</v>
+        <v>0.6868</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>61.84</v>
+        <v>47.94</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>46.13</v>
+        <v>76.98</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>51.46</v>
+        <v>65.61</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>88.23999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>0.3414</v>
+        <v>0.154</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>0.1638</v>
+        <v>0.1312</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.1253</v>
+        <v>0.156</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.1694</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.3004</v>
+        <v>0.3894</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>55.64</v>
+        <v>66.87</v>
       </c>
       <c r="AD10" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -1549,40 +1540,40 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1</v>
+        <v>0.4162</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.9688</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.75</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.8409</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0.3263</v>
+        <v>0.2753</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.3092</v>
+        <v>0.4187</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4688</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>1</v>
@@ -1591,42 +1582,42 @@
         <v>1</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>0.9794</v>
+        <v>0.9796</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>1</v>
+        <v>0.9558</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>67.72</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>73.13</v>
+        <v>72.22</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>61.56</v>
+        <v>78.42</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>89.51000000000001</v>
+        <v>78.84</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>0.0915</v>
+        <v>0.0038</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.1029</v>
+        <v>0.1333</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2362</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>0.3373</v>
+        <v>0.2422</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>0.3754</v>
+        <v>0.3846</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>71.58</v>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
+        <v>73.04000000000001</v>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1647,40 +1638,40 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0</v>
+        <v>0.1919</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.6944</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5357</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.217</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0.766</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>0.1235</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0</v>
+        <v>0.0291</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>1</v>
@@ -1692,39 +1683,39 @@
         <v>1</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>1</v>
+        <v>0.7197</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>74.93000000000001</v>
+        <v>68.03</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>52.01</v>
+        <v>59.67</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>52.09</v>
+        <v>69.12</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>74.17</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>0.0987</v>
+        <v>0.2687</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.2772</v>
+        <v>0.0475</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.1966</v>
+        <v>0.0914</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>0.195</v>
+        <v>0.183</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.2325</v>
+        <v>0.4094</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>62.29</v>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
+        <v>64.91</v>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -1745,86 +1736,86 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.2357</v>
+        <v>0.2861</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.4167</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.2083</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>0.6442</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.8409</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0.3874</v>
+        <v>0.4041</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1562</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>0.1546</v>
+        <v>0.55</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>1</v>
+        <v>0.7702</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>59.47</v>
+        <v>69.38</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>27.24</v>
+        <v>77.48</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>42.63</v>
+        <v>71.95</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>84</v>
+        <v>62.73</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>0.5704</v>
+        <v>0.0187</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.1749</v>
+        <v>0.1044</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.2146</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>0.0057</v>
+        <v>0.318</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>0.2291</v>
+        <v>0.3442</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>44.37</v>
-      </c>
-      <c r="AD13" s="5" t="inlineStr">
-        <is>
-          <t>及格</t>
+        <v>72.88</v>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -1843,84 +1834,84 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.6623</v>
+        <v>0.3564</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.875</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.1734</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0.0151</v>
+        <v>0.0413</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>1</v>
+        <v>0.6944</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.9375</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>0.4124</v>
+        <v>0.9125</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>1</v>
+        <v>0.9816</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>64.28</v>
+        <v>56.89</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>44.1</v>
+        <v>69.58</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>25</v>
+        <v>62.49</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>80.16</v>
+        <v>65.31</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.3442</v>
+        <v>0.1281</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.2609</v>
+        <v>0.1976</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>0.1541</v>
+        <v>0.216</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>0.045</v>
+        <v>0.1172</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>0.1958</v>
+        <v>0.3411</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>50.59</v>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -1941,86 +1932,86 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.7444</v>
+        <v>0.3308</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="2" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.9091</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.4688</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0.2399</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0.8418</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>0.2471</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="R15" s="2" t="n">
-        <v>0.6186</v>
+        <v>1</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>74.81</v>
+        <v>69.63</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>51.45</v>
+        <v>72.47</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>63.73</v>
+        <v>81.27</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>87.12</v>
+        <v>60.85</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>0.0209</v>
+        <v>0.0117</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>0.2903</v>
+        <v>0.1535</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>0.345</v>
+        <v>0.2047</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>0.117</v>
+        <v>0.2929</v>
       </c>
       <c r="AB15" s="2" t="n">
-        <v>0.2268</v>
+        <v>0.3371</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>63.47</v>
+        <v>71.8</v>
       </c>
       <c r="AD15" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -2039,16 +2030,16 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.7802</v>
+        <v>0.3391</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.8</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>0.8333</v>
@@ -2057,66 +2048,66 @@
         <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0.585</v>
+        <v>0.7153</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.0513</v>
+        <v>0.3851</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.3125</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>0.9278</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>1</v>
+        <v>0.5686</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>81.23999999999999</v>
+        <v>46.32</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>43.88</v>
+        <v>77.94</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>89.17</v>
+        <v>73.44</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.1079</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>0.1344</v>
+        <v>0.0751</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.0825</v>
+        <v>0.1495</v>
       </c>
       <c r="AA16" s="2" t="n">
-        <v>0.4242</v>
+        <v>0.2718</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>0.3305</v>
+        <v>0.3957</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>73.27</v>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
+        <v>71.05</v>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2137,86 +2128,86 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.3726</v>
+        <v>0.2681</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.9038</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.9722</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.7806</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0.0907</v>
+        <v>0.1446</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.375</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.7812</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>0.3093</v>
+        <v>0.375</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>1</v>
+        <v>0.9167</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>71.34</v>
+        <v>56.92</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>46.91</v>
+        <v>83.78</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>40.29</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>85.09</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>0.3371</v>
+        <v>0.0751</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>0.0997</v>
+        <v>0.1302</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>0.1395</v>
+        <v>0.1268</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>0.1834</v>
+        <v>0.0798</v>
       </c>
       <c r="AB17" s="2" t="n">
-        <v>0.2402</v>
+        <v>0.588</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>56.66</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="AD17" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -2235,84 +2226,84 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.3814</v>
+        <v>0.3625</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.9375</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.1141</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>0.9091</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0.2968</v>
+        <v>0.4421</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.1562</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.4124</v>
+        <v>0.775</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>77.64</v>
+        <v>62.47</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>66.01000000000001</v>
+        <v>84.42</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>65.65000000000001</v>
+        <v>77.11</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>85.81999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.0659</v>
+        <v>0.0129</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>0.1695</v>
+        <v>0.1104</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.1076</v>
+        <v>0.1536</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>0.2412</v>
+        <v>0.2883</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>0.4158</v>
+        <v>0.4347</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>71.23999999999999</v>
-      </c>
-      <c r="AD18" s="3" t="inlineStr">
+        <v>75.26000000000001</v>
+      </c>
+      <c r="AD18" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2333,84 +2324,84 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1</v>
+        <v>0.3824</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.6944</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.4688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.2778</v>
+        <v>0.9</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>0.8409</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0.0402</v>
+        <v>0.2197</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>0</v>
+        <v>0.0463</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v>0.8333</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>1</v>
+        <v>0.6479</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>83.98999999999999</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>51.85</v>
+        <v>50.69</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>35.3</v>
+        <v>62.66</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>55.55</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>0.2849</v>
+        <v>0.312</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.0959</v>
+        <v>0.066</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>0.015</v>
+        <v>0.1554</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>0.3454</v>
+        <v>0.2395</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>0.2589</v>
+        <v>0.2271</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>61.54</v>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
+        <v>58.49</v>
+      </c>
+      <c r="AD19" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -2431,84 +2422,84 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1</v>
+        <v>0.3276</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.9286</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.921</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0.1841</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>0.9524</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0.1204</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>0.2222</v>
-      </c>
-      <c r="N20" s="2" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="O20" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.2577</v>
+        <v>0.75</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>1</v>
+        <v>0.9591</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>67.72</v>
+        <v>60.27</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>66.06999999999999</v>
+        <v>86.41</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>46.32</v>
+        <v>46.59</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>62.15</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>0.1047</v>
+        <v>0.0607</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>0.2715</v>
+        <v>0.2013</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.1383</v>
+        <v>0.1669</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>0.0871</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0.3984</v>
+        <v>0.4836</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>65.52</v>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
+        <v>70.67</v>
+      </c>
+      <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2529,84 +2520,84 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1</v>
+        <v>0.3691</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.9091</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.75</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0.8409</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0.465</v>
+        <v>0.4921</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.375</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.4688</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.5669999999999999</v>
+        <v>1</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>1</v>
+        <v>0.8759</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>77.81</v>
+        <v>60.07</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>72.22</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>60.12</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="W21" s="2" t="n">
-        <v>86.8</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="X21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1868</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.2131</v>
+        <v>0.2947</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>0.3361</v>
+        <v>0.1733</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>0.3604</v>
+        <v>0.3452</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="AD21" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2627,84 +2618,84 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.5278</v>
+        <v>0.3442</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.6944</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.8294</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>0.9091</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0.731</v>
+        <v>0.504</v>
       </c>
       <c r="M22" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="2" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>0.5155</v>
-      </c>
-      <c r="S22" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T22" s="2" t="n">
-        <v>78.67</v>
+        <v>68.64</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>71.43000000000001</v>
+        <v>88.56</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>44.72</v>
+        <v>71.72</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>86.62</v>
+        <v>68.09</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0.0283</v>
+        <v>0.0141</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>0.1555</v>
+        <v>0.0765</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.4924</v>
+        <v>0.2</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>0.232</v>
+        <v>0.5675</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>71.02</v>
-      </c>
-      <c r="AD22" s="3" t="inlineStr">
+        <v>78.38</v>
+      </c>
+      <c r="AD22" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2725,86 +2716,86 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.7539</v>
+        <v>0.3466</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.875</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.2083</v>
+        <v>0.7143</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.7897999999999999</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2778</v>
+        <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.9524</v>
+        <v>0.8409</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0.1721</v>
+        <v>0.2319</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0.2222</v>
+        <v>0.375</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.3125</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>1</v>
+        <v>0.8756</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>86.83</v>
+        <v>58.04</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>41.42</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>58.19</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="W23" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>72.22</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>0.3409</v>
+        <v>0.0186</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.0358</v>
+        <v>0.2558</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.2402</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>0.1853</v>
+        <v>0.1545</v>
       </c>
       <c r="AB23" s="2" t="n">
-        <v>0.3516</v>
+        <v>0.3308</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>60.86</v>
+        <v>67.75</v>
       </c>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -2823,84 +2814,84 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.8201000000000001</v>
+        <v>0.3587</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.625</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.8592</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0.3745</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>0.2222</v>
-      </c>
-      <c r="N24" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="O24" s="2" t="n">
-        <v>0.3333</v>
-      </c>
       <c r="P24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>1</v>
+        <v>0.7615</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>75.39</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>66.33</v>
+        <v>62.73</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>59.98</v>
+        <v>70.69</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>82.90000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1121</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>0.066</v>
+        <v>0.1837</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.1878</v>
+        <v>0.1688</v>
       </c>
       <c r="AA24" s="2" t="n">
-        <v>0.409</v>
+        <v>0.1754</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>0.2503</v>
+        <v>0.36</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>69.61</v>
-      </c>
-      <c r="AD24" s="3" t="inlineStr">
+        <v>66.75</v>
+      </c>
+      <c r="AD24" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2921,84 +2912,84 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.9878</v>
+        <v>0.1487</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>0.9801</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.9853</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
+        <v>0.7812</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0.8391</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="P25" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0.3568</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>0.3037</v>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>0.2778</v>
-      </c>
-      <c r="O25" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P25" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Q25" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.8247</v>
+        <v>1</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>83.87</v>
+        <v>65.31</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>58.53</v>
+        <v>75.7</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>88.5</v>
+        <v>54.63</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>0</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>0.1873</v>
+        <v>0.1296</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>0.1141</v>
+        <v>0.1866</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>0.4322</v>
+        <v>0.2317</v>
       </c>
       <c r="AB25" s="2" t="n">
-        <v>0.2665</v>
+        <v>0.3729</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>71.67</v>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
+        <v>69.95</v>
+      </c>
+      <c r="AD25" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -3169,86 +3160,86 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.7339</v>
+        <v>0.3442</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1</v>
+        <v>0.8097</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.5556</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="2" t="n">
         <v>0.625</v>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0.1709</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>0.5556</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="N27" s="2" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>0.6667</v>
-      </c>
       <c r="P27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>1</v>
+        <v>0.3332</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>74.75</v>
+        <v>29.99</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>50.94</v>
+        <v>69.86</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>86.39</v>
+        <v>84.39</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>0.0329</v>
+        <v>0.252</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>0.2541</v>
+        <v>0.1979</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>0.2706</v>
+        <v>0.1056</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>0.0968</v>
+        <v>0.0436</v>
       </c>
       <c r="AB27" s="2" t="n">
-        <v>0.3456</v>
+        <v>0.4008</v>
       </c>
       <c r="AC27" s="2" t="n">
-        <v>66.86</v>
+        <v>60.89</v>
       </c>
       <c r="AD27" s="3" t="inlineStr">
         <is>
-          <t>良好</t>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -3267,43 +3258,43 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.7101</v>
+        <v>0.3717</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1</v>
+        <v>0.8239</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.6929</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.4167</v>
+        <v>0.7237</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.3558</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0.9091</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0.9022</v>
+        <v>0.9227</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.2847</v>
+        <v>0.436</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.4688</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1</v>
+        <v>0.9722</v>
       </c>
       <c r="Q28" s="2" t="n">
         <v>1</v>
@@ -3312,39 +3303,39 @@
         <v>1</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>1</v>
+        <v>0.0048</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>64.48999999999999</v>
+        <v>30.38</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>46.37</v>
+        <v>73.03</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>68.78</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>68.03</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>0.2848</v>
+        <v>0.2225</v>
       </c>
       <c r="Y28" s="2" t="n">
-        <v>0.1286</v>
+        <v>0.1615</v>
       </c>
       <c r="Z28" s="2" t="n">
-        <v>0.1541</v>
+        <v>0.1433</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.1235</v>
+        <v>0.1359</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>0.309</v>
+        <v>0.3368</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>59.23</v>
-      </c>
-      <c r="AD28" s="4" t="inlineStr">
+        <v>61.93</v>
+      </c>
+      <c r="AD28" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -3365,40 +3356,40 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.2157</v>
+        <v>0.3318</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.9722</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.8333</v>
+        <v>0.4688</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.3228</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.3006</v>
+        <v>0.4019</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.7812</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>1</v>
@@ -3410,39 +3401,39 @@
         <v>1</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>1</v>
+        <v>0.1319</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>75.48999999999999</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>69.09</v>
+        <v>59.67</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>65.76000000000001</v>
+        <v>84.14</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>68.39</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>0.0321</v>
+        <v>0.2287</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>0.1271</v>
+        <v>0.0609</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>0.122</v>
+        <v>0.1389</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>0.4027</v>
+        <v>0.1692</v>
       </c>
       <c r="AB29" s="2" t="n">
-        <v>0.3161</v>
+        <v>0.4023</v>
       </c>
       <c r="AC29" s="2" t="n">
-        <v>72.48999999999999</v>
-      </c>
-      <c r="AD29" s="3" t="inlineStr">
+        <v>65.69</v>
+      </c>
+      <c r="AD29" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -3463,84 +3454,84 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.0538</v>
+        <v>0.1391</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.9312</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.2256</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0.9091</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0.9735</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.2879</v>
+        <v>0.4163</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.9375</v>
       </c>
       <c r="P30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>1</v>
+        <v>0.9375</v>
       </c>
       <c r="R30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>1</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>74.93000000000001</v>
+        <v>59.76</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>52.21</v>
+        <v>58.24</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>69.53</v>
+        <v>84.78</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>89.65000000000001</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>0.043</v>
+        <v>0.2534</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>0.2822</v>
+        <v>0.0562</v>
       </c>
       <c r="Z30" s="2" t="n">
-        <v>0.1983</v>
+        <v>0.1573</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.2378</v>
+        <v>0.1685</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>0.2386</v>
+        <v>0.3646</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="AD30" s="4" t="inlineStr">
+        <v>63.75</v>
+      </c>
+      <c r="AD30" s="3" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
@@ -3561,40 +3552,40 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.2155</v>
+        <v>0.2506</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.6944</v>
+        <v>0.8214</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.625</v>
+        <v>0.9375</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.5643</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5556</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0.8409</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0.6099</v>
+        <v>0.6819</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.3835</v>
+        <v>0.5033</v>
       </c>
       <c r="N31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>0.6667</v>
+        <v>1</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>1</v>
@@ -3603,42 +3594,42 @@
         <v>1</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0.6701</v>
+        <v>1</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>1</v>
+        <v>0.7016</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>75.48999999999999</v>
+        <v>47.53</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>56.5</v>
+        <v>86.16</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>82.86</v>
+        <v>86.14</v>
       </c>
       <c r="W31" s="2" t="n">
-        <v>87.45</v>
+        <v>74.03</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>0.0322</v>
+        <v>0.0854</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.158</v>
+        <v>0.118</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.3016</v>
+        <v>0.1144</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>0.1888</v>
+        <v>0.1048</v>
       </c>
       <c r="AB31" s="2" t="n">
-        <v>0.3194</v>
+        <v>0.5773</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>68.92</v>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
+        <v>74.13</v>
+      </c>
+      <c r="AD31" s="4" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -3915,10 +3906,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.5333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -3928,10 +3919,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.4</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="5">
@@ -3941,10 +3932,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">

--- a/output/problem1_results.xlsx
+++ b/output/problem1_results.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
         <bgColor rgb="00BDD7EE"/>
       </patternFill>
@@ -56,6 +68,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
         <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +107,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,7 +764,7 @@
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -833,9 +860,9 @@
       <c r="AC3" s="2" t="n">
         <v>55.85</v>
       </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -931,9 +958,9 @@
       <c r="AC4" s="2" t="n">
         <v>61.26</v>
       </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -1029,9 +1056,9 @@
       <c r="AC5" s="2" t="n">
         <v>59.98</v>
       </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD5" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -1127,9 +1154,9 @@
       <c r="AC6" s="2" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD6" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -1225,9 +1252,9 @@
       <c r="AC7" s="2" t="n">
         <v>66.48999999999999</v>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD7" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -1323,9 +1350,9 @@
       <c r="AC8" s="2" t="n">
         <v>61.26</v>
       </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1448,7 @@
       <c r="AC9" s="2" t="n">
         <v>71.8</v>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1519,9 +1546,9 @@
       <c r="AC10" s="2" t="n">
         <v>66.87</v>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD10" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -1617,9 +1644,9 @@
       <c r="AC11" s="2" t="n">
         <v>73.04000000000001</v>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD11" s="7" t="inlineStr">
+        <is>
+          <t>优秀</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1744,7 @@
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1840,7 @@
       <c r="AC13" s="2" t="n">
         <v>72.88</v>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AD13" s="6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -1913,7 +1940,7 @@
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2036,7 @@
       <c r="AC15" s="2" t="n">
         <v>71.8</v>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AD15" s="6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2107,7 +2134,7 @@
       <c r="AC16" s="2" t="n">
         <v>71.05</v>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AD16" s="6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2205,9 +2232,9 @@
       <c r="AC17" s="2" t="n">
         <v>74.26000000000001</v>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD17" s="7" t="inlineStr">
+        <is>
+          <t>优秀</t>
         </is>
       </c>
     </row>
@@ -2303,9 +2330,9 @@
       <c r="AC18" s="2" t="n">
         <v>75.26000000000001</v>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD18" s="7" t="inlineStr">
+        <is>
+          <t>优秀</t>
         </is>
       </c>
     </row>
@@ -2401,9 +2428,9 @@
       <c r="AC19" s="2" t="n">
         <v>58.49</v>
       </c>
-      <c r="AD19" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2526,7 @@
       <c r="AC20" s="2" t="n">
         <v>70.67</v>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AD20" s="6" t="inlineStr">
         <is>
           <t>良好</t>
         </is>
@@ -2597,9 +2624,9 @@
       <c r="AC21" s="2" t="n">
         <v>70.15000000000001</v>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD21" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -2695,9 +2722,9 @@
       <c r="AC22" s="2" t="n">
         <v>78.38</v>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD22" s="7" t="inlineStr">
+        <is>
+          <t>优秀</t>
         </is>
       </c>
     </row>
@@ -2793,9 +2820,9 @@
       <c r="AC23" s="2" t="n">
         <v>67.75</v>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD23" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -2891,9 +2918,9 @@
       <c r="AC24" s="2" t="n">
         <v>66.75</v>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD24" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -2989,9 +3016,9 @@
       <c r="AC25" s="2" t="n">
         <v>69.95</v>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD25" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -3237,9 +3264,9 @@
       <c r="AC27" s="2" t="n">
         <v>60.89</v>
       </c>
-      <c r="AD27" s="3" t="inlineStr">
-        <is>
-          <t>中等</t>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3364,7 @@
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -3433,9 +3460,9 @@
       <c r="AC29" s="2" t="n">
         <v>65.69</v>
       </c>
-      <c r="AD29" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3560,7 @@
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
-          <t>中等</t>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -3629,9 +3656,9 @@
       <c r="AC31" s="2" t="n">
         <v>74.13</v>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
-        <is>
-          <t>良好</t>
+      <c r="AD31" s="7" t="inlineStr">
+        <is>
+          <t>优秀</t>
         </is>
       </c>
     </row>
@@ -3893,10 +3920,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="3">
@@ -3906,10 +3933,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.6</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="4">
@@ -3919,10 +3946,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.3667</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="5">
@@ -3932,10 +3959,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -3945,10 +3972,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">

--- a/output/problem1_results.xlsx
+++ b/output/problem1_results.xlsx
@@ -706,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.4409</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0.842</v>
@@ -736,7 +736,7 @@
         <v>43.39</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>70.31999999999999</v>
+        <v>70.16</v>
       </c>
       <c r="V2" s="2" t="n">
         <v>78.81999999999999</v>
@@ -745,13 +745,13 @@
         <v>72.39</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>0.1073</v>
+        <v>0.1133</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.2143</v>
+        <v>0.2054</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>0.2572</v>
+        <v>0.2601</v>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.09180000000000001</v>
@@ -760,7 +760,7 @@
         <v>0.3294</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>64.29000000000001</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>32.44</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>60.1</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>76.43000000000001</v>
@@ -843,7 +843,7 @@
         <v>70.06</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>0.3612</v>
+        <v>0.3163</v>
       </c>
       <c r="Y3" s="2" t="n">
         <v>0.1481</v>
@@ -852,13 +852,13 @@
         <v>0.1024</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.1042</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>0.3257</v>
+        <v>0.329</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>55.85</v>
+        <v>58.14</v>
       </c>
       <c r="AD3" s="4" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.6727</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0.6843</v>
@@ -932,7 +932,7 @@
         <v>57.58</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>60.1</v>
+        <v>64.89</v>
       </c>
       <c r="V4" s="2" t="n">
         <v>66.09</v>
@@ -941,7 +941,7 @@
         <v>69.55</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>0.1623</v>
+        <v>0.1174</v>
       </c>
       <c r="Y4" s="2" t="n">
         <v>0.2405</v>
@@ -950,17 +950,17 @@
         <v>0.1621</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.1668</v>
+        <v>0.2117</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>0.2683</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>61.26</v>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>不及格</t>
+        <v>63.51</v>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>及格</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
         <v>0.95</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.5409</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0.0793</v>
@@ -1030,7 +1030,7 @@
         <v>38.28</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>69</v>
+        <v>69.95</v>
       </c>
       <c r="V5" s="2" t="n">
         <v>69.02</v>
@@ -1042,19 +1042,19 @@
         <v>0.1687</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>0.3073</v>
+        <v>0.2848</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>0.1504</v>
+        <v>0.1653</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.0477</v>
+        <v>0.0552</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>0.3259</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>59.98</v>
+        <v>60.43</v>
       </c>
       <c r="AD5" s="4" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>58.26</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>71.15000000000001</v>
+        <v>72.59</v>
       </c>
       <c r="V7" s="2" t="n">
         <v>74.81999999999999</v>
@@ -1244,13 +1244,13 @@
         <v>0.1365</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>0.1215</v>
+        <v>0.0766</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>0.3891</v>
+        <v>0.4339</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>66.48999999999999</v>
+        <v>67.16</v>
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0.6455</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0.7491</v>
@@ -1324,7 +1324,7 @@
         <v>30.73</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>72.59</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V8" s="2" t="n">
         <v>74.06</v>
@@ -1339,16 +1339,16 @@
         <v>0.2354</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>0.1415</v>
+        <v>0.143</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>0.0506</v>
+        <v>0.0939</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>0.3703</v>
+        <v>0.3254</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>61.26</v>
+        <v>60.56</v>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
         <v>47.14</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>86.16</v>
+        <v>85.69</v>
       </c>
       <c r="V9" s="2" t="n">
         <v>75.36</v>
@@ -1434,10 +1434,10 @@
         <v>0.121</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>0.132</v>
+        <v>0.1467</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>0.1104</v>
+        <v>0.0958</v>
       </c>
       <c r="AA9" s="2" t="n">
         <v>0.0723</v>
@@ -1446,7 +1446,7 @@
         <v>0.5643</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>71.8</v>
+        <v>71.58</v>
       </c>
       <c r="AD9" s="6" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.5773</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0.7418</v>
@@ -1520,7 +1520,7 @@
         <v>47.94</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>76.98</v>
+        <v>74.75</v>
       </c>
       <c r="V10" s="2" t="n">
         <v>65.61</v>
@@ -1535,16 +1535,16 @@
         <v>0.1312</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>0.156</v>
+        <v>0.1809</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>0.1694</v>
+        <v>0.1894</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>0.3894</v>
+        <v>0.3446</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>66.87</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="AD10" s="5" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0.2753</v>
@@ -1618,7 +1618,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>72.22</v>
+        <v>71.75</v>
       </c>
       <c r="V11" s="2" t="n">
         <v>78.42</v>
@@ -1630,10 +1630,10 @@
         <v>0.0038</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>0.1333</v>
+        <v>0.1479</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0.2362</v>
+        <v>0.2215</v>
       </c>
       <c r="AA11" s="2" t="n">
         <v>0.2422</v>
@@ -1642,7 +1642,7 @@
         <v>0.3846</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>73.04000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="AD11" s="7" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.4773</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>1</v>
@@ -1716,7 +1716,7 @@
         <v>68.03</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>59.67</v>
+        <v>56.55</v>
       </c>
       <c r="V12" s="2" t="n">
         <v>69.12</v>
@@ -1728,19 +1728,19 @@
         <v>0.2687</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>0.0475</v>
+        <v>0.0553</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>0.0914</v>
+        <v>0.1284</v>
       </c>
       <c r="AA12" s="2" t="n">
         <v>0.183</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.4094</v>
+        <v>0.3645</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>64.91</v>
+        <v>63.44</v>
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>0.6</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0.4041</v>
@@ -1814,7 +1814,7 @@
         <v>69.38</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>77.48</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="V13" s="2" t="n">
         <v>71.95</v>
@@ -1826,10 +1826,10 @@
         <v>0.0187</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>0.1044</v>
+        <v>0.119</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>0.2146</v>
+        <v>0.2</v>
       </c>
       <c r="AA13" s="2" t="n">
         <v>0.318</v>
@@ -1838,7 +1838,7 @@
         <v>0.3442</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>72.88</v>
+        <v>72.66</v>
       </c>
       <c r="AD13" s="6" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.2727</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0.0413</v>
@@ -1912,7 +1912,7 @@
         <v>56.89</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>69.58</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="V14" s="2" t="n">
         <v>62.49</v>
@@ -1921,10 +1921,10 @@
         <v>65.31</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>0.1281</v>
+        <v>0.101</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>0.1976</v>
+        <v>0.2247</v>
       </c>
       <c r="Z14" s="2" t="n">
         <v>0.216</v>
@@ -1936,7 +1936,7 @@
         <v>0.3411</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>64.54000000000001</v>
+        <v>65.09</v>
       </c>
       <c r="AD14" s="3" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>69.63</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>72.47</v>
+        <v>73.91</v>
       </c>
       <c r="V15" s="2" t="n">
         <v>81.27</v>
@@ -2028,13 +2028,13 @@
         <v>0.2047</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>0.2929</v>
+        <v>0.2481</v>
       </c>
       <c r="AB15" s="2" t="n">
-        <v>0.3371</v>
+        <v>0.382</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>71.8</v>
+        <v>72.47</v>
       </c>
       <c r="AD15" s="6" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.4773</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0.7153</v>
@@ -2108,7 +2108,7 @@
         <v>46.32</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>83.04000000000001</v>
+        <v>79.92</v>
       </c>
       <c r="V16" s="2" t="n">
         <v>77.94</v>
@@ -2120,23 +2120,23 @@
         <v>0.1079</v>
       </c>
       <c r="Y16" s="2" t="n">
-        <v>0.0751</v>
+        <v>0.0829</v>
       </c>
       <c r="Z16" s="2" t="n">
-        <v>0.1495</v>
+        <v>0.1866</v>
       </c>
       <c r="AA16" s="2" t="n">
         <v>0.2718</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>0.3957</v>
+        <v>0.3509</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>71.05</v>
-      </c>
-      <c r="AD16" s="6" t="inlineStr">
-        <is>
-          <t>良好</t>
+        <v>69.58</v>
+      </c>
+      <c r="AD16" s="5" t="inlineStr">
+        <is>
+          <t>中等</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.2727</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0.1446</v>
@@ -2206,7 +2206,7 @@
         <v>56.92</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>83.78</v>
+        <v>84.94</v>
       </c>
       <c r="V17" s="2" t="n">
         <v>77.76000000000001</v>
@@ -2215,10 +2215,10 @@
         <v>72.79000000000001</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>0.0751</v>
+        <v>0.048</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>0.1302</v>
+        <v>0.1573</v>
       </c>
       <c r="Z17" s="2" t="n">
         <v>0.1268</v>
@@ -2230,7 +2230,7 @@
         <v>0.588</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>74.26000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="AD17" s="7" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.9091</v>
+        <v>0.4091</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>1</v>
@@ -2304,7 +2304,7 @@
         <v>62.47</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>84.42</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="V18" s="2" t="n">
         <v>77.11</v>
@@ -2313,22 +2313,22 @@
         <v>65.5</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>0.0129</v>
+        <v>0.0234</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>0.1104</v>
+        <v>0.1276</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>0.1536</v>
+        <v>0.1708</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>0.2883</v>
+        <v>0.2435</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>0.4347</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>75.26000000000001</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="AD18" s="7" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>70.45999999999999</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>50.69</v>
+        <v>54.09</v>
       </c>
       <c r="V19" s="2" t="n">
         <v>62.66</v>
@@ -2414,19 +2414,19 @@
         <v>0.312</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>0.066</v>
+        <v>0.0436</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>0.1554</v>
+        <v>0.133</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>0.2395</v>
+        <v>0.2457</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>0.2271</v>
+        <v>0.2658</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>58.49</v>
+        <v>60.08</v>
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0.1841</v>
@@ -2500,7 +2500,7 @@
         <v>60.27</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>86.41</v>
+        <v>85.94</v>
       </c>
       <c r="V20" s="2" t="n">
         <v>46.59</v>
@@ -2512,10 +2512,10 @@
         <v>0.0607</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>0.2013</v>
+        <v>0.2159</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>0.1669</v>
+        <v>0.1523</v>
       </c>
       <c r="AA20" s="2" t="n">
         <v>0.08749999999999999</v>
@@ -2524,7 +2524,7 @@
         <v>0.4836</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>70.67</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="AD20" s="6" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0.4921</v>
@@ -2598,7 +2598,7 @@
         <v>60.07</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>72.22</v>
+        <v>71.75</v>
       </c>
       <c r="V21" s="2" t="n">
         <v>77.98999999999999</v>
@@ -2610,10 +2610,10 @@
         <v>0</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>0.1868</v>
+        <v>0.2014</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>0.2947</v>
+        <v>0.2801</v>
       </c>
       <c r="AA21" s="2" t="n">
         <v>0.1733</v>
@@ -2622,11 +2622,11 @@
         <v>0.3452</v>
       </c>
       <c r="AC21" s="2" t="n">
-        <v>70.15000000000001</v>
-      </c>
-      <c r="AD21" s="5" t="inlineStr">
-        <is>
-          <t>中等</t>
+        <v>69.94</v>
+      </c>
+      <c r="AD21" s="6" t="inlineStr">
+        <is>
+          <t>良好</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.9091</v>
+        <v>0.4091</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0.504</v>
@@ -2696,7 +2696,7 @@
         <v>68.64</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>88.56</v>
+        <v>85.8</v>
       </c>
       <c r="V22" s="2" t="n">
         <v>71.72</v>
@@ -2705,22 +2705,22 @@
         <v>68.09</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0245</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>0.0765</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>0.142</v>
+        <v>0.1592</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1551</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>0.5675</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>78.38</v>
+        <v>77.09</v>
       </c>
       <c r="AD22" s="7" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0.2319</v>
@@ -2794,7 +2794,7 @@
         <v>58.04</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>70.31999999999999</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="V23" s="2" t="n">
         <v>74.76000000000001</v>
@@ -2806,10 +2806,10 @@
         <v>0.0186</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>0.2558</v>
+        <v>0.2705</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>0.2402</v>
+        <v>0.2256</v>
       </c>
       <c r="AA23" s="2" t="n">
         <v>0.1545</v>
@@ -2818,7 +2818,7 @@
         <v>0.3308</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>67.75</v>
+        <v>67.53</v>
       </c>
       <c r="AD23" s="5" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.4409</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0.2826</v>
@@ -2892,7 +2892,7 @@
         <v>70.20999999999999</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>62.73</v>
+        <v>62.58</v>
       </c>
       <c r="V24" s="2" t="n">
         <v>70.69</v>
@@ -2901,13 +2901,13 @@
         <v>69.98</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>0.1121</v>
+        <v>0.1181</v>
       </c>
       <c r="Y24" s="2" t="n">
-        <v>0.1837</v>
+        <v>0.1748</v>
       </c>
       <c r="Z24" s="2" t="n">
-        <v>0.1688</v>
+        <v>0.1717</v>
       </c>
       <c r="AA24" s="2" t="n">
         <v>0.1754</v>
@@ -2916,7 +2916,7 @@
         <v>0.36</v>
       </c>
       <c r="AC24" s="2" t="n">
-        <v>66.75</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="AD24" s="5" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0.8391</v>
@@ -2990,7 +2990,7 @@
         <v>65.31</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>74.23999999999999</v>
+        <v>73.77</v>
       </c>
       <c r="V25" s="2" t="n">
         <v>75.7</v>
@@ -3002,10 +3002,10 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>0.1296</v>
+        <v>0.1442</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>0.1866</v>
+        <v>0.172</v>
       </c>
       <c r="AA25" s="2" t="n">
         <v>0.2317</v>
@@ -3014,7 +3014,7 @@
         <v>0.3729</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>69.95</v>
+        <v>69.73</v>
       </c>
       <c r="AD25" s="5" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>30.38</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>73.03</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="V28" s="2" t="n">
         <v>81.84999999999999</v>
@@ -3354,17 +3354,17 @@
         <v>0.1433</v>
       </c>
       <c r="AA28" s="2" t="n">
-        <v>0.1359</v>
+        <v>0.091</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>0.3368</v>
+        <v>0.3817</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
-        <is>
-          <t>及格</t>
+        <v>62.61</v>
+      </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>不及格</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
         <v>59.76</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>58.24</v>
+        <v>59.67</v>
       </c>
       <c r="V30" s="2" t="n">
         <v>84.78</v>
@@ -3550,13 +3550,13 @@
         <v>0.1573</v>
       </c>
       <c r="AA30" s="2" t="n">
-        <v>0.1685</v>
+        <v>0.1236</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>0.3646</v>
+        <v>0.4095</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>63.75</v>
+        <v>64.42</v>
       </c>
       <c r="AD30" s="3" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.8409</v>
+        <v>0.3409</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0.6819</v>
@@ -3630,7 +3630,7 @@
         <v>47.53</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>86.16</v>
+        <v>85.69</v>
       </c>
       <c r="V31" s="2" t="n">
         <v>86.14</v>
@@ -3642,10 +3642,10 @@
         <v>0.0854</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>0.118</v>
+        <v>0.1326</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>0.1144</v>
+        <v>0.0998</v>
       </c>
       <c r="AA31" s="2" t="n">
         <v>0.1048</v>
@@ -3654,7 +3654,7 @@
         <v>0.5773</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>74.13</v>
+        <v>73.91</v>
       </c>
       <c r="AD31" s="7" t="inlineStr">
         <is>
